--- a/public/plantilla-pqrs-comunidad.xlsx
+++ b/public/plantilla-pqrs-comunidad.xlsx
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
+  </numFmts>
   <fonts count="20">
     <font>
       <name val="Calibri"/>
@@ -554,19 +557,19 @@
     <xf numFmtId="4" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -615,7 +618,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -668,7 +671,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">

--- a/public/plantilla-pqrs-comunidad.xlsx
+++ b/public/plantilla-pqrs-comunidad.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="9" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PQRS Comunidad" sheetId="1" state="visible" r:id="rId1"/>

--- a/public/plantilla-pqrs-comunidad.xlsx
+++ b/public/plantilla-pqrs-comunidad.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PQRS Comunidad" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,9 +16,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -163,6 +163,10 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -529,7 +533,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -560,7 +564,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -636,7 +640,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -757,6 +761,45 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1219,6 +1262,7 @@
   <cols>
     <col width="12.77734375" customWidth="1" style="27" min="1" max="1"/>
     <col width="13" customWidth="1" style="27" min="2" max="3"/>
+    <col width="13" customWidth="1" style="27" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="27" min="4" max="4"/>
     <col width="10" customWidth="1" style="27" min="5" max="5"/>
     <col width="15.77734375" customWidth="1" style="27" min="6" max="6"/>
@@ -1386,20 +1430,20 @@
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="22" t="n"/>
+      <c r="C11" s="97" t="n"/>
+      <c r="D11" s="98" t="n"/>
+      <c r="E11" s="98" t="n"/>
+      <c r="F11" s="98" t="n"/>
+      <c r="G11" s="99" t="n"/>
       <c r="H11" s="88" t="inlineStr">
         <is>
           <t>PQRS N°</t>
         </is>
       </c>
       <c r="I11" s="22" t="n"/>
-      <c r="J11" s="32" t="n"/>
-      <c r="K11" s="25" t="n"/>
-      <c r="L11" s="22" t="n"/>
+      <c r="J11" s="100" t="n"/>
+      <c r="K11" s="98" t="n"/>
+      <c r="L11" s="99" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="27">
       <c r="A12" s="88" t="inlineStr">
@@ -1408,20 +1452,20 @@
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="22" t="n"/>
+      <c r="C12" s="97" t="n"/>
+      <c r="D12" s="98" t="n"/>
+      <c r="E12" s="98" t="n"/>
+      <c r="F12" s="98" t="n"/>
+      <c r="G12" s="99" t="n"/>
       <c r="H12" s="88" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="22" t="n"/>
-      <c r="J12" s="24" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="22" t="n"/>
+      <c r="J12" s="97" t="n"/>
+      <c r="K12" s="98" t="n"/>
+      <c r="L12" s="99" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="27">
       <c r="A13" s="88" t="inlineStr">
@@ -1430,24 +1474,24 @@
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="22" t="n"/>
+      <c r="C13" s="101" t="n"/>
+      <c r="D13" s="99" t="n"/>
       <c r="E13" s="88" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
       <c r="F13" s="22" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="22" t="n"/>
+      <c r="G13" s="102" t="n"/>
+      <c r="H13" s="99" t="n"/>
       <c r="I13" s="88" t="inlineStr">
         <is>
           <t>Recibió</t>
         </is>
       </c>
       <c r="J13" s="22" t="n"/>
-      <c r="K13" s="24" t="n"/>
-      <c r="L13" s="22" t="n"/>
+      <c r="K13" s="97" t="n"/>
+      <c r="L13" s="99" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="27">
       <c r="A14" s="88" t="inlineStr">
@@ -1456,23 +1500,23 @@
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
-      <c r="C14" s="32" t="n"/>
-      <c r="D14" s="22" t="n"/>
+      <c r="C14" s="100" t="n"/>
+      <c r="D14" s="99" t="n"/>
       <c r="E14" s="88" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
       <c r="F14" s="22" t="n"/>
-      <c r="G14" s="32" t="n"/>
-      <c r="H14" s="22" t="n"/>
+      <c r="G14" s="100" t="n"/>
+      <c r="H14" s="99" t="n"/>
       <c r="I14" s="88" t="inlineStr">
         <is>
           <t>Fecha límite de respuesta</t>
         </is>
       </c>
       <c r="J14" s="22" t="n"/>
-      <c r="K14" s="23">
+      <c r="K14" s="103">
         <f>IF(C13="","",WORKDAY(C13,15))</f>
         <v/>
       </c>
@@ -1503,20 +1547,20 @@
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="22" t="n"/>
+      <c r="C16" s="97" t="n"/>
+      <c r="D16" s="98" t="n"/>
+      <c r="E16" s="98" t="n"/>
+      <c r="F16" s="98" t="n"/>
+      <c r="G16" s="99" t="n"/>
       <c r="H16" s="88" t="inlineStr">
         <is>
           <t>Documento</t>
         </is>
       </c>
       <c r="I16" s="22" t="n"/>
-      <c r="J16" s="32" t="n"/>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="22" t="n"/>
+      <c r="J16" s="100" t="n"/>
+      <c r="K16" s="98" t="n"/>
+      <c r="L16" s="99" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1" s="27">
       <c r="A17" s="88" t="inlineStr">
@@ -1525,20 +1569,20 @@
         </is>
       </c>
       <c r="B17" s="22" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="22" t="n"/>
+      <c r="C17" s="97" t="n"/>
+      <c r="D17" s="98" t="n"/>
+      <c r="E17" s="98" t="n"/>
+      <c r="F17" s="98" t="n"/>
+      <c r="G17" s="99" t="n"/>
       <c r="H17" s="88" t="inlineStr">
         <is>
           <t>Teléfono</t>
         </is>
       </c>
       <c r="I17" s="22" t="n"/>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="25" t="n"/>
-      <c r="L17" s="22" t="n"/>
+      <c r="J17" s="100" t="n"/>
+      <c r="K17" s="98" t="n"/>
+      <c r="L17" s="99" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1" s="27">
       <c r="A18" s="88" t="inlineStr">
@@ -1547,20 +1591,20 @@
         </is>
       </c>
       <c r="B18" s="22" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="n"/>
-      <c r="G18" s="22" t="n"/>
+      <c r="C18" s="97" t="n"/>
+      <c r="D18" s="98" t="n"/>
+      <c r="E18" s="98" t="n"/>
+      <c r="F18" s="98" t="n"/>
+      <c r="G18" s="99" t="n"/>
       <c r="H18" s="88" t="inlineStr">
         <is>
           <t>¿Desea respuesta?</t>
         </is>
       </c>
       <c r="I18" s="22" t="n"/>
-      <c r="J18" s="32" t="n"/>
-      <c r="K18" s="25" t="n"/>
-      <c r="L18" s="22" t="n"/>
+      <c r="J18" s="100" t="n"/>
+      <c r="K18" s="98" t="n"/>
+      <c r="L18" s="99" t="n"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="27">
       <c r="A19" s="77" t="inlineStr">
@@ -1581,28 +1625,28 @@
       <c r="L19" s="18" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="27">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="104" t="inlineStr">
         <is>
           <t>☐ Ruido</t>
         </is>
       </c>
       <c r="B20" s="17" t="n"/>
       <c r="C20" s="18" t="n"/>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="104" t="inlineStr">
         <is>
           <t>☐ Polvo</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
       <c r="F20" s="18" t="n"/>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G20" s="104" t="inlineStr">
         <is>
           <t>☐ Vibraciones o daños en vivienda</t>
         </is>
       </c>
       <c r="H20" s="17" t="n"/>
       <c r="I20" s="18" t="n"/>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J20" s="104" t="inlineStr">
         <is>
           <t>☐ Tránsito y movilidad</t>
         </is>
@@ -1611,28 +1655,28 @@
       <c r="L20" s="18" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="27">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="104" t="inlineStr">
         <is>
           <t>☐ Residuos o escombros</t>
         </is>
       </c>
       <c r="B21" s="17" t="n"/>
       <c r="C21" s="18" t="n"/>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="104" t="inlineStr">
         <is>
           <t>☐ Agua o alcantarillado</t>
         </is>
       </c>
       <c r="E21" s="17" t="n"/>
       <c r="F21" s="18" t="n"/>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G21" s="104" t="inlineStr">
         <is>
           <t>☐ Seguridad en la vía</t>
         </is>
       </c>
       <c r="H21" s="17" t="n"/>
       <c r="I21" s="18" t="n"/>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J21" s="104" t="inlineStr">
         <is>
           <t>☐ Otro:</t>
         </is>
@@ -1647,16 +1691,16 @@
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
-      <c r="C22" s="40" t="n"/>
-      <c r="D22" s="25" t="n"/>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="25" t="n"/>
-      <c r="G22" s="25" t="n"/>
-      <c r="H22" s="25" t="n"/>
-      <c r="I22" s="25" t="n"/>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="25" t="n"/>
-      <c r="L22" s="22" t="n"/>
+      <c r="C22" s="105" t="n"/>
+      <c r="D22" s="98" t="n"/>
+      <c r="E22" s="98" t="n"/>
+      <c r="F22" s="98" t="n"/>
+      <c r="G22" s="98" t="n"/>
+      <c r="H22" s="98" t="n"/>
+      <c r="I22" s="98" t="n"/>
+      <c r="J22" s="98" t="n"/>
+      <c r="K22" s="98" t="n"/>
+      <c r="L22" s="99" t="n"/>
     </row>
     <row r="23" ht="25.95" customHeight="1" s="27">
       <c r="A23" s="36" t="inlineStr">
@@ -1701,16 +1745,16 @@
         </is>
       </c>
       <c r="B25" s="22" t="n"/>
-      <c r="C25" s="40" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="25" t="n"/>
-      <c r="G25" s="25" t="n"/>
-      <c r="H25" s="25" t="n"/>
-      <c r="I25" s="25" t="n"/>
-      <c r="J25" s="25" t="n"/>
-      <c r="K25" s="25" t="n"/>
-      <c r="L25" s="22" t="n"/>
+      <c r="C25" s="105" t="n"/>
+      <c r="D25" s="98" t="n"/>
+      <c r="E25" s="98" t="n"/>
+      <c r="F25" s="98" t="n"/>
+      <c r="G25" s="98" t="n"/>
+      <c r="H25" s="98" t="n"/>
+      <c r="I25" s="98" t="n"/>
+      <c r="J25" s="98" t="n"/>
+      <c r="K25" s="98" t="n"/>
+      <c r="L25" s="99" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1" s="27">
       <c r="A26" s="88" t="inlineStr">
@@ -1719,20 +1763,20 @@
         </is>
       </c>
       <c r="B26" s="22" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="25" t="n"/>
-      <c r="E26" s="25" t="n"/>
-      <c r="F26" s="25" t="n"/>
-      <c r="G26" s="22" t="n"/>
+      <c r="C26" s="97" t="n"/>
+      <c r="D26" s="98" t="n"/>
+      <c r="E26" s="98" t="n"/>
+      <c r="F26" s="98" t="n"/>
+      <c r="G26" s="99" t="n"/>
       <c r="H26" s="88" t="inlineStr">
         <is>
           <t>Fecha de respuesta</t>
         </is>
       </c>
       <c r="I26" s="22" t="n"/>
-      <c r="J26" s="23" t="n"/>
-      <c r="K26" s="25" t="n"/>
-      <c r="L26" s="22" t="n"/>
+      <c r="J26" s="101" t="n"/>
+      <c r="K26" s="98" t="n"/>
+      <c r="L26" s="99" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1" s="27">
       <c r="A27" s="88" t="inlineStr">
@@ -1741,20 +1785,20 @@
         </is>
       </c>
       <c r="B27" s="22" t="n"/>
-      <c r="C27" s="24" t="n"/>
-      <c r="D27" s="25" t="n"/>
-      <c r="E27" s="25" t="n"/>
-      <c r="F27" s="25" t="n"/>
-      <c r="G27" s="22" t="n"/>
+      <c r="C27" s="97" t="n"/>
+      <c r="D27" s="98" t="n"/>
+      <c r="E27" s="98" t="n"/>
+      <c r="F27" s="98" t="n"/>
+      <c r="G27" s="99" t="n"/>
       <c r="H27" s="88" t="inlineStr">
         <is>
           <t>Compromiso con la comunidad</t>
         </is>
       </c>
       <c r="I27" s="22" t="n"/>
-      <c r="J27" s="24" t="n"/>
-      <c r="K27" s="25" t="n"/>
-      <c r="L27" s="22" t="n"/>
+      <c r="J27" s="97" t="n"/>
+      <c r="K27" s="98" t="n"/>
+      <c r="L27" s="99" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="27">
       <c r="A28" s="77" t="inlineStr">
@@ -1781,24 +1825,24 @@
         </is>
       </c>
       <c r="B29" s="22" t="n"/>
-      <c r="C29" s="32" t="n"/>
-      <c r="D29" s="22" t="n"/>
+      <c r="C29" s="100" t="n"/>
+      <c r="D29" s="99" t="n"/>
       <c r="E29" s="88" t="inlineStr">
         <is>
           <t>Fecha de cierre</t>
         </is>
       </c>
       <c r="F29" s="22" t="n"/>
-      <c r="G29" s="23" t="n"/>
-      <c r="H29" s="22" t="n"/>
+      <c r="G29" s="101" t="n"/>
+      <c r="H29" s="99" t="n"/>
       <c r="I29" s="88" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
       <c r="J29" s="22" t="n"/>
-      <c r="K29" s="32" t="n"/>
-      <c r="L29" s="22" t="n"/>
+      <c r="K29" s="100" t="n"/>
+      <c r="L29" s="99" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="27">
       <c r="A30" s="77" t="inlineStr">
@@ -1851,24 +1895,24 @@
         </is>
       </c>
       <c r="B32" s="18" t="n"/>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="18" t="n"/>
+      <c r="C32" s="106" t="n"/>
+      <c r="D32" s="107" t="n"/>
       <c r="E32" s="82" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F32" s="18" t="n"/>
-      <c r="G32" s="19" t="n"/>
-      <c r="H32" s="18" t="n"/>
+      <c r="G32" s="106" t="n"/>
+      <c r="H32" s="107" t="n"/>
       <c r="I32" s="82" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J32" s="18" t="n"/>
-      <c r="K32" s="19" t="n"/>
-      <c r="L32" s="18" t="n"/>
+      <c r="K32" s="106" t="n"/>
+      <c r="L32" s="107" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1" s="27">
       <c r="A33" s="82" t="inlineStr">
@@ -1877,24 +1921,24 @@
         </is>
       </c>
       <c r="B33" s="18" t="n"/>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="18" t="n"/>
+      <c r="C33" s="106" t="n"/>
+      <c r="D33" s="107" t="n"/>
       <c r="E33" s="82" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F33" s="18" t="n"/>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="18" t="n"/>
+      <c r="G33" s="106" t="n"/>
+      <c r="H33" s="107" t="n"/>
       <c r="I33" s="82" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J33" s="18" t="n"/>
-      <c r="K33" s="19" t="n"/>
-      <c r="L33" s="18" t="n"/>
+      <c r="K33" s="106" t="n"/>
+      <c r="L33" s="107" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1" s="27">
       <c r="A34" s="82" t="inlineStr">
@@ -1903,24 +1947,24 @@
         </is>
       </c>
       <c r="B34" s="18" t="n"/>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="18" t="n"/>
+      <c r="C34" s="106" t="n"/>
+      <c r="D34" s="107" t="n"/>
       <c r="E34" s="82" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="F34" s="18" t="n"/>
-      <c r="G34" s="19" t="n"/>
-      <c r="H34" s="18" t="n"/>
+      <c r="G34" s="106" t="n"/>
+      <c r="H34" s="107" t="n"/>
       <c r="I34" s="82" t="inlineStr">
         <is>
           <t>Documento:</t>
         </is>
       </c>
       <c r="J34" s="18" t="n"/>
-      <c r="K34" s="19" t="n"/>
-      <c r="L34" s="18" t="n"/>
+      <c r="K34" s="106" t="n"/>
+      <c r="L34" s="107" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1934,6 +1978,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="97">
     <mergeCell ref="K33:L33"/>
     <mergeCell ref="J27:L27"/>
